--- a/controle_equipamentos.xlsx
+++ b/controle_equipamentos.xlsx
@@ -1070,7 +1070,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Lucas Faria  |  Matrícula cbk3574  |  github.com/lucasdpr/controle-equipamentos</t>
+          <t>Lucas Gabriel de Paula Rafael  |  Matrícula cbk3574  |  github.com/lucasdpr/controle-equipamentos</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>Autor: Lucas Faria  |  Matrícula cbk3574  |  github.com/lucasdpr/controle-equipamentos</t>
+          <t>Autor: Lucas Gabriel de Paula Rafael  |  Matrícula cbk3574  |  github.com/lucasdpr/controle-equipamentos</t>
         </is>
       </c>
     </row>

--- a/controle_equipamentos.xlsx
+++ b/controle_equipamentos.xlsx
@@ -1063,7 +1063,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <f>"Dados do robô até: "&amp;IF(MAX(Historico!$A$2:$A$5000)=0,"nenhum e-mail processado ainda",TEXT(MAX(Historico!$A$2:$A$5000),"dd/mm/yyyy"))&amp;"   |   Hoje: "&amp;TEXT(TODAY(),"dd/mm/yyyy")</f>
+        <f>"Dados do robô até: "&amp;IF(MAX(Historico!$A$2:$A$5000)=0,"nenhum e-mail processado ainda",RIGHT("0"&amp;DAY(MAX(Historico!$A$2:$A$5000)),2)&amp;"/"&amp;RIGHT("0"&amp;MONTH(MAX(Historico!$A$2:$A$5000)),2)&amp;"/"&amp;YEAR(MAX(Historico!$A$2:$A$5000)))&amp;"   |   Hoje: "&amp;RIGHT("0"&amp;DAY(TODAY()),2)&amp;"/"&amp;RIGHT("0"&amp;MONTH(TODAY()),2)&amp;"/"&amp;YEAR(TODAY())</f>
         <v/>
       </c>
     </row>
